--- a/data/trans_orig/Q5407-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2007</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92069</t>
+          <t>91023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105640</t>
+          <t>105678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117557</t>
+          <t>116311</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134456</t>
+          <t>134965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214835</t>
+          <t>214625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>237490</t>
+          <t>237426</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22834</t>
+          <t>23452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43282</t>
+          <t>41579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53467</t>
+          <t>54594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121338</t>
+          <t>121114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135768</t>
+          <t>136588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130370</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153509</t>
+          <t>154650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259019</t>
+          <t>258662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285770</t>
+          <t>285963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16250</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>28492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89748</t>
+          <t>88515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100953</t>
+          <t>100986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105237</t>
+          <t>105505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122194</t>
+          <t>122628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200859</t>
+          <t>200531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221627</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20425</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36575</t>
+          <t>35848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>48467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117348</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130743</t>
+          <t>129894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161874</t>
+          <t>161492</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183464</t>
+          <t>182965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>284093</t>
+          <t>283118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>310529</t>
+          <t>309457</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>53759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64499</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98609</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101932</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>143944</t>
+          <t>142200</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>437973</t>
+          <t>437558</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>462787</t>
+          <t>462859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>537075</t>
+          <t>537481</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>576837</t>
+          <t>578079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>984044</t>
+          <t>985298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1031457</t>
+          <t>1035390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2012</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32437</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47705</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116196</t>
+          <t>116470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130344</t>
+          <t>130686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114859</t>
+          <t>115364</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137351</t>
+          <t>136733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236325</t>
+          <t>235012</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>263870</t>
+          <t>263197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>43934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>35614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63335</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>26719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42847</t>
+          <t>43264</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111416</t>
+          <t>111414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133929</t>
+          <t>133599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114983</t>
+          <t>114403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140691</t>
+          <t>142616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233361</t>
+          <t>233046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268989</t>
+          <t>268456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31869</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38889</t>
+          <t>38625</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72580</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>91934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92458</t>
+          <t>92420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114062</t>
+          <t>114710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171466</t>
+          <t>173021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201747</t>
+          <t>201500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>26171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37583</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47281</t>
+          <t>46946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>63292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146421</t>
+          <t>145937</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>177521</t>
+          <t>176662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203941</t>
+          <t>204606</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>309275</t>
+          <t>313793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>344092</t>
+          <t>345440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49044</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71919</t>
+          <t>73389</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>108386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>101386</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147630</t>
+          <t>147138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>72759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86014</t>
+          <t>84986</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>122128</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136634</t>
+          <t>134633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>185209</t>
+          <t>183096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>449764</t>
+          <t>450990</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>488342</t>
+          <t>487987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>524561</t>
+          <t>524506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>574031</t>
+          <t>573159</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>991325</t>
+          <t>989582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1050990</t>
+          <t>1050794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2016</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>55190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107115</t>
+          <t>107221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123269</t>
+          <t>123191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>115855</t>
+          <t>113393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140061</t>
+          <t>139873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230333</t>
+          <t>230904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>259850</t>
+          <t>258335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39300</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>29032</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48874</t>
+          <t>49949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42920</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>72714</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126550</t>
+          <t>127701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145274</t>
+          <t>145183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150606</t>
+          <t>149923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178814</t>
+          <t>178735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284077</t>
+          <t>283470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318454</t>
+          <t>318797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,47 +6684,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>16674</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9394</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26805</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16674</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9284</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25884</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>34448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>46235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94967</t>
+          <t>95311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108084</t>
+          <t>108341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89017</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112378</t>
+          <t>112567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190305</t>
+          <t>188648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217877</t>
+          <t>216413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30420</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68843</t>
+          <t>68128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144083</t>
+          <t>143575</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160600</t>
+          <t>160806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>176746</t>
+          <t>176521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205838</t>
+          <t>205772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>327986</t>
+          <t>328560</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>361167</t>
+          <t>360447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39614</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73698</t>
+          <t>71849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70277</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107258</t>
+          <t>109238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65152</t>
+          <t>65481</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>111117</t>
+          <t>114610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155950</t>
+          <t>160447</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>159542</t>
+          <t>160084</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>215193</t>
+          <t>212281</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492462</t>
+          <t>490224</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>523067</t>
+          <t>524113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562737</t>
+          <t>559428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>615236</t>
+          <t>612118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1061556</t>
+          <t>1063801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1123318</t>
+          <t>1126045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de subir y bajar las escaleras en 2023</t>
+          <t>Población según si es capaz de subir y bajar las escaleras en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29588</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41555</t>
+          <t>41224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59090</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115575</t>
+          <t>115171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129295</t>
+          <t>129732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109946</t>
+          <t>109082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125800</t>
+          <t>125153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228349</t>
+          <t>229842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250707</t>
+          <t>250585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>18443</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35656</t>
+          <t>35674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51965</t>
+          <t>51632</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>65919</t>
+          <t>67562</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129347</t>
+          <t>128138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142801</t>
+          <t>142524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140632</t>
+          <t>142033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159789</t>
+          <t>160205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274061</t>
+          <t>273258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297618</t>
+          <t>297434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38424</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7976</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>41773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>67660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73790</t>
+          <t>73972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108578</t>
+          <t>108616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>123004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257291</t>
+          <t>255586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347486</t>
+          <t>348821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383924</t>
+          <t>384482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475266</t>
+          <t>474811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36516</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32169</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>50619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27903</t>
+          <t>29061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41044</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>60242</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59565</t>
+          <t>60539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83912</t>
+          <t>85737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164424</t>
+          <t>163482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180157</t>
+          <t>180330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>184336</t>
+          <t>183490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206331</t>
+          <t>205441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>353598</t>
+          <t>351899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>382291</t>
+          <t>380660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51468</t>
+          <t>54579</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124203</t>
+          <t>124378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89073</t>
+          <t>87297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160899</t>
+          <t>160311</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49934</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73775</t>
+          <t>74595</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85721</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>200148</t>
+          <t>198117</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137222</t>
+          <t>139888</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>252087</t>
+          <t>252228</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532246</t>
+          <t>532550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>561651</t>
+          <t>562169</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>710044</t>
+          <t>712522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>890520</t>
+          <t>885516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1272695</t>
+          <t>1272442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1454037</t>
+          <t>1458269</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5407-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5407-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>22792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>16476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>35445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91023</t>
+          <t>92696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105678</t>
+          <t>105807</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116311</t>
+          <t>115957</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134965</t>
+          <t>135250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214625</t>
+          <t>214302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>237426</t>
+          <t>237631</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41579</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54594</t>
+          <t>54669</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121114</t>
+          <t>120872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136588</t>
+          <t>136209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>129565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154650</t>
+          <t>154019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258662</t>
+          <t>258329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285963</t>
+          <t>286248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88515</t>
+          <t>90718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100986</t>
+          <t>101521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>105505</t>
+          <t>104885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122628</t>
+          <t>122562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200531</t>
+          <t>200764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221040</t>
+          <t>221300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35848</t>
+          <t>37669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117934</t>
+          <t>117344</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129894</t>
+          <t>130410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161492</t>
+          <t>161191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182965</t>
+          <t>183504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>283118</t>
+          <t>283985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>309457</t>
+          <t>309370</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>52113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64379</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53759</t>
+          <t>55443</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99112</t>
+          <t>97670</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99345</t>
+          <t>102096</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142200</t>
+          <t>141687</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>437558</t>
+          <t>435923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>462859</t>
+          <t>462814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>537481</t>
+          <t>535947</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>578079</t>
+          <t>577143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>985298</t>
+          <t>985709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1035390</t>
+          <t>1033098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47469</t>
+          <t>45998</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116470</t>
+          <t>116187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130686</t>
+          <t>130635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>115364</t>
+          <t>116062</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136733</t>
+          <t>137305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>235012</t>
+          <t>234733</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>263197</t>
+          <t>263773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26434</t>
+          <t>25095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43934</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>35335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62989</t>
+          <t>62395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26719</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>42005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34904</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60136</t>
+          <t>60606</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111414</t>
+          <t>111773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133599</t>
+          <t>133727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114403</t>
+          <t>114882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142616</t>
+          <t>140843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233046</t>
+          <t>235547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268456</t>
+          <t>266708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>37848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41043</t>
+          <t>41423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>73134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91934</t>
+          <t>91952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92420</t>
+          <t>93957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114710</t>
+          <t>116103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173021</t>
+          <t>174599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201500</t>
+          <t>201226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46946</t>
+          <t>46258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>36636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63292</t>
+          <t>64990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126448</t>
+          <t>125283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>145937</t>
+          <t>146226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>178165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204606</t>
+          <t>203107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>313793</t>
+          <t>311626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>345440</t>
+          <t>344183</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49318</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73389</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108386</t>
+          <t>108566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101386</t>
+          <t>103593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147138</t>
+          <t>147589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40904</t>
+          <t>40717</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72759</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84986</t>
+          <t>84631</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122128</t>
+          <t>124369</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>134633</t>
+          <t>133683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>183096</t>
+          <t>182821</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>450990</t>
+          <t>449916</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>487987</t>
+          <t>487638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>524506</t>
+          <t>525941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>573159</t>
+          <t>575007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>989582</t>
+          <t>988587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1050794</t>
+          <t>1050326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33137</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46649</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31804</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>56747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107221</t>
+          <t>107261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123191</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113393</t>
+          <t>116660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139873</t>
+          <t>141053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230904</t>
+          <t>229177</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258335</t>
+          <t>258452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>36839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127701</t>
+          <t>127383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145183</t>
+          <t>144726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149923</t>
+          <t>150653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178735</t>
+          <t>178089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>283470</t>
+          <t>284094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318797</t>
+          <t>317361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>26746</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>34617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95311</t>
+          <t>95214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108341</t>
+          <t>108376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88769</t>
+          <t>90266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112567</t>
+          <t>113822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188648</t>
+          <t>190002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216413</t>
+          <t>217578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28425</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>55317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39632</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143575</t>
+          <t>143309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160806</t>
+          <t>160516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>176521</t>
+          <t>176226</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205772</t>
+          <t>204731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>328560</t>
+          <t>325099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>360447</t>
+          <t>359815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>44076</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40666</t>
+          <t>40326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>72594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68665</t>
+          <t>69643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109238</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65481</t>
+          <t>63121</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114610</t>
+          <t>111568</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>160447</t>
+          <t>158653</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>160084</t>
+          <t>159991</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>212281</t>
+          <t>213256</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490224</t>
+          <t>492349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>524113</t>
+          <t>523682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>559428</t>
+          <t>562186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>612118</t>
+          <t>614039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1063801</t>
+          <t>1065959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1126045</t>
+          <t>1126778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46136</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>29760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41224</t>
+          <t>44155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48972</t>
+          <t>51596</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40964</t>
+          <t>43360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>61421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122988</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115171</t>
+          <t>129483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>143901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117708</t>
+          <t>125622</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109082</t>
+          <t>116901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125153</t>
+          <t>134076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240696</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229842</t>
+          <t>249956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250585</t>
+          <t>273981</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,54%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>147352</t>
+          <t>162310</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147352</t>
+          <t>162310</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147352</t>
+          <t>162310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>326515</t>
+          <t>353339</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>326515</t>
+          <t>353339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326515</t>
+          <t>353339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23692</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44296</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43221</t>
+          <t>47532</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51632</t>
+          <t>56762</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>60847</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67562</t>
+          <t>73955</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>152560</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128138</t>
+          <t>144590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142524</t>
+          <t>159112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>150965</t>
+          <t>167375</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142033</t>
+          <t>157589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160205</t>
+          <t>178127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>287275</t>
+          <t>319935</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273258</t>
+          <t>304826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297434</t>
+          <t>331687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>217877</t>
+          <t>241412</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217877</t>
+          <t>241412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217877</t>
+          <t>241412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>419616</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>419616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377991</t>
+          <t>419616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -9289,27 +9289,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19661</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67660</t>
+          <t>38712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>45606</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73972</t>
+          <t>56377</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>116655</t>
+          <t>136662</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108616</t>
+          <t>127151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123004</t>
+          <t>144150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>317440</t>
+          <t>126611</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255586</t>
+          <t>115989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348821</t>
+          <t>134599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>434095</t>
+          <t>263273</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384482</t>
+          <t>250542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474811</t>
+          <t>275673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28989</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50619</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50170</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>44597</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60242</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>76873</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>64437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85737</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172787</t>
+          <t>181975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163482</t>
+          <t>172483</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180330</t>
+          <t>189770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>195345</t>
+          <t>207183</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183490</t>
+          <t>194450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205441</t>
+          <t>218201</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>368133</t>
+          <t>389158</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>351899</t>
+          <t>371838</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380660</t>
+          <t>403022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>274504</t>
+          <t>294209</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>274504</t>
+          <t>294209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>274504</t>
+          <t>294209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>479534</t>
+          <t>509298</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>479534</t>
+          <t>509298</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479534</t>
+          <t>509298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>39792</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50537</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>95244</t>
+          <t>104621</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>91211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124378</t>
+          <t>119105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>135036</t>
+          <t>146199</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87297</t>
+          <t>130743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160311</t>
+          <t>163636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60914</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>53627</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74595</t>
+          <t>79206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>154505</t>
+          <t>169538</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>152408</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>198117</t>
+          <t>186730</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>215419</t>
+          <t>234923</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>139888</t>
+          <t>213735</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>252228</t>
+          <t>257702</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>548742</t>
+          <t>608424</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>532550</t>
+          <t>591798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>562169</t>
+          <t>623513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>781459</t>
+          <t>626792</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>712522</t>
+          <t>604134</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>885516</t>
+          <t>646744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1330200</t>
+          <t>1235216</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1272442</t>
+          <t>1208269</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1458269</t>
+          <t>1259414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>649448</t>
+          <t>715387</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649448</t>
+          <t>715387</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649448</t>
+          <t>715387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1031208</t>
+          <t>900951</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1031208</t>
+          <t>900951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1031208</t>
+          <t>900951</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1680655</t>
+          <t>1616338</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1680655</t>
+          <t>1616338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1680655</t>
+          <t>1616338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
